--- a/criteria.xlsx
+++ b/criteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Previous Document Folder\Projects\Aravinda\Photography Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F847F95E-3131-4A32-92DC-13435529EB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220E1CDF-2BF7-4E41-A553-8CC08BEF14A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D85D41E3-257E-47C4-8A91-CE79E7D9E562}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{D85D41E3-257E-47C4-8A91-CE79E7D9E562}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -521,7 +521,7 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.44140625" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
     <col min="3" max="3" width="15.5546875" customWidth="1"/>
     <col min="4" max="4" width="14.21875" customWidth="1"/>
